--- a/Result/profitability/5904.xlsx
+++ b/Result/profitability/5904.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>6.75875</v>
+        <v>6.86875</v>
       </c>
       <c r="N2" t="n">
-        <v>43.24125</v>
+        <v>43.10875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9325</v>
+        <v>6.05625</v>
       </c>
       <c r="N3" t="n">
-        <v>41.1825</v>
+        <v>41.01125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>5.105</v>
+        <v>5.18875</v>
       </c>
       <c r="N4" t="n">
-        <v>38.85</v>
+        <v>38.91125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.318750000000001</v>
+        <v>4.640000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>37.23875</v>
+        <v>37.52625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.70875</v>
+        <v>3.77875</v>
       </c>
       <c r="N6" t="n">
-        <v>35.41625</v>
+        <v>35.29625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.82875</v>
+        <v>2.725</v>
       </c>
       <c r="N7" t="n">
-        <v>33.42875</v>
+        <v>33.09375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.765</v>
+        <v>1.62125</v>
       </c>
       <c r="N8" t="n">
-        <v>30.82875</v>
+        <v>30.805</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6932</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3817</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3115</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1077</v>
+      </c>
+      <c r="K75" t="n">
+        <v>868</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.68875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>45.37375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1236559139784946</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1900000000000048</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.004210059827166046</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4605734767025089</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.299999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05393996247654775</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
